--- a/data/600104_上汽集团_财务数据.xlsx
+++ b/data/600104_上汽集团_财务数据.xlsx
@@ -12905,7 +12905,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
@@ -20748,7 +20748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -20778,8 +20778,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20826,22 +20824,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -20851,75 +20849,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -20953,58 +20941,52 @@
         <v>3.787631445963044</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>-0.04456808306126049</v>
+      <c r="J2" s="3" t="n">
+        <v>60.17114997206752</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>60.17114997206752</v>
-      </c>
-      <c r="L2" s="3" t="n">
         <v>1.113149240381188</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.9885973112385923</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>151.0742839169816</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>12.29381608409077</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>29.28301493511604</v>
+        <v>19.93966132392468</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>19.93966132392468</v>
+        <v>1.263284244899037</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>18.05446913825224</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1.263284244899037</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>2.254246941575091</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>0.2584450666169333</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>-5907000000</v>
       </c>
+      <c r="X2" s="3" t="n">
+        <v>1.19483062916474</v>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
       <c r="Z2" s="3" t="n">
-        <v>1.19483062916474</v>
+        <v>2.315888096207856</v>
       </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>2.315888096207856</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21040,64 +21022,58 @@
       <c r="I3" s="3" t="n">
         <v>1.516919234750592</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>0.01669443912943039</v>
-      </c>
-      <c r="K3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>62.39204016955689</v>
       </c>
+      <c r="K3" s="6" t="n">
+        <v>0.9973808933097682</v>
+      </c>
       <c r="L3" s="6" t="n">
-        <v>0.9973808933097682</v>
-      </c>
-      <c r="M3" s="6" t="n">
         <v>0.8693874001529517</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>165.901156167082</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>13.72654536287721</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>26.2265552244196</v>
+        <v>19.50803213460646</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>19.50803213460646</v>
+        <v>1.305660700352431</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>18.45393720473602</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>1.305660700352431</v>
-      </c>
+        <v>2.380018746342887</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>2.380018746342887</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>14.97425557137525</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>7.18178822522551</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>14.97425557137525</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>7.18178822522551</v>
+        <v>22.48531428281221</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>0.5157685225036471</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>22.48531428281221</v>
-      </c>
-      <c r="X3" s="6" t="n">
-        <v>0.5157685225036471</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-1111000000</v>
       </c>
+      <c r="X3" s="3" t="n">
+        <v>1.118971949927104</v>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="n">
-        <v>1.118971949927104</v>
+        <v>2.075236716308604</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.075236716308604</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21133,64 +21109,58 @@
       <c r="I4" s="3" t="n">
         <v>1.733276069910029</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>0.0220179725502965</v>
+      <c r="J4" s="3" t="n">
+        <v>63.62660807133641</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>63.62660807133641</v>
-      </c>
-      <c r="L4" s="3" t="n">
         <v>1.094257378904864</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>0.9519939757145996</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>174.9262433267772</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>14.15671781959187</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>25.42962320699691</v>
+        <v>16.17986418387484</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>16.17986418387484</v>
+        <v>1.178549345368641</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>22.24987774364526</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>1.178549345368641</v>
-      </c>
+        <v>2.105063189845931</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>2.105063189845931</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>3.455624634880809</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>2.734873976641671</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>3.455624634880809</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>2.734873976641671</v>
+        <v>8.187187039153708</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>0.1854366783935758</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>8.187187039153708</v>
-      </c>
-      <c r="X4" s="6" t="n">
-        <v>0.1854366783935758</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>-22999000000</v>
       </c>
+      <c r="X4" s="3" t="n">
+        <v>1.115016649884041</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
       <c r="Z4" s="3" t="n">
-        <v>1.115016649884041</v>
+        <v>2.052684922593226</v>
       </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.052684922593226</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21226,64 +21196,58 @@
       <c r="I5" s="3" t="n">
         <v>1.620528018237068</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.002948063603560102</v>
+      <c r="J5" s="3" t="n">
+        <v>64.57938170305404</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>64.57938170305404</v>
-      </c>
-      <c r="L5" s="3" t="n">
         <v>1.10448290093193</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>0.9869404476634767</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>182.3208349953464</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>15.21090218572399</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>23.66723522407986</v>
+        <v>14.6525530025101</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>14.6525530025101</v>
+        <v>1.012840492257989</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>24.56909727187672</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>1.012840492257989</v>
-      </c>
+        <v>1.713843167722175</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.713843167722175</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>-6.883100546026181</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-27.09605970264018</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>-6.883100546026181</v>
+        <v>8.503519552358931</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-27.09605970264018</v>
+        <v>1.311233587402371</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>8.503519552358931</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>1.311233587402371</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>19337000000</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.8407547185277597</v>
       </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>1.811401472581387</v>
+      </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>1.811401472581387</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21319,64 +21283,58 @@
       <c r="I6" s="3" t="n">
         <v>1.852594105500434</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>0.07149217291764422</v>
+      <c r="J6" s="3" t="n">
+        <v>66.27834003143303</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>66.27834003143303</v>
-      </c>
-      <c r="L6" s="3" t="n">
         <v>1.108226133525419</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="L6" s="6" t="n">
         <v>0.9723929502587672</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>196.5459406981657</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>15.27420309934576</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>23.56915104889628</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>11.78617377985977</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0.8175755836504466</v>
+      </c>
       <c r="Q6" s="3" t="n">
-        <v>30.54426370457634</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0.8175755836504466</v>
-      </c>
+        <v>1.342282449744471</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>1.342282449744471</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>-12.52070867131158</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-17.28831118070393</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>-12.52070867131158</v>
+        <v>8.251416111230812</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-17.28831118070393</v>
+        <v>1.285389016490599</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>8.251416111230812</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>1.285389016490599</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>22380000000</v>
       </c>
-      <c r="Z6" s="6" t="n">
+      <c r="X6" s="6" t="n">
         <v>0.8819452816632559</v>
       </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>1.568202502887362</v>
+      </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.568202502887362</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -21412,64 +21370,58 @@
       <c r="I7" s="3" t="n">
         <v>2.588250918796126</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>0.074243031507635</v>
+      <c r="J7" s="3" t="n">
+        <v>64.14409934094793</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>64.14409934094793</v>
+        <v>1.134298754789471</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.134298754789471</v>
+        <v>1.016425207240244</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.016425207240244</v>
+        <v>178.894123873456</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>15.36220746485156</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>23.43413215995638</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>12.23111346068047</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.8276413553061364</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>29.43313388084389</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.8276413553061364</v>
-      </c>
+        <v>1.367756619173926</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.367756619173926</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="3" t="n">
         <v>5.099567701097283</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>16.28648658208666</v>
       </c>
-      <c r="W7" s="6" t="n">
+      <c r="U7" s="6" t="n">
         <v>-0.2710419125204614</v>
       </c>
+      <c r="V7" s="6" t="n">
+        <v>0.6368556235026029</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>2873000000</v>
+      </c>
       <c r="X7" s="6" t="n">
-        <v>0.6368556235026029</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>2873000000</v>
-      </c>
-      <c r="Z7" s="6" t="n">
         <v>0.8492098583209607</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>1.695248039298054</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>1.695248039298054</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -21505,64 +21457,58 @@
       <c r="I8" s="3" t="n">
         <v>2.500864263275667</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.1060220871642847</v>
+      <c r="J8" s="3" t="n">
+        <v>66.03397410582896</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>66.03397410582896</v>
-      </c>
-      <c r="L8" s="3" t="n">
         <v>1.070205432234937</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>0.9074497908911255</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>194.4118346714243</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>11.95340459579104</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>30.11694259280415</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>10.12159189485393</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0.756136535137916</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>35.56752769127482</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.756136535137916</v>
-      </c>
+        <v>1.279283461651937</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>1.279283461651937</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>-5.122563171764613</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-32.70044454685387</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>-5.122563171764613</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-32.70044454685387</v>
+        <v>7.981477179654125</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.4161075367729464</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>7.981477179654125</v>
+        <v>-13430000000</v>
       </c>
       <c r="X8" s="6" t="n">
-        <v>0.4161075367729464</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>-13430000000</v>
-      </c>
-      <c r="Z8" s="6" t="n">
         <v>0.7401404033392036</v>
       </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>1.46529647527416</v>
+      </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>1.46529647527416</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -21596,56 +21542,50 @@
       <c r="I9" s="3" t="n">
         <v>2.528977662880826</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.02157590001456009</v>
-      </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="3" t="n">
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="3" t="n">
         <v>1.1318299722344</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>0.9517116030980565</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>193.5635609655096</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>9.954614883548409</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>36.16413133118364</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>7.825074935988543</v>
       </c>
+      <c r="P9" s="4" t="inlineStr"/>
       <c r="Q9" s="3" t="n">
-        <v>46.00594920111408</v>
+        <v>1.208545217935718</v>
       </c>
       <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="3" t="n">
-        <v>1.208545217935718</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="6" t="n">
+      <c r="S9" s="6" t="n">
         <v>0.7228394199804755</v>
       </c>
+      <c r="T9" s="3" t="n">
+        <v>-12.17990661134342</v>
+      </c>
+      <c r="U9" s="4" t="inlineStr"/>
       <c r="V9" s="3" t="n">
-        <v>-12.17990661134342</v>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="3" t="n">
         <v>2.110322705806311</v>
       </c>
-      <c r="Y9" s="3" t="n">
+      <c r="W9" s="3" t="n">
         <v>22924000000</v>
       </c>
-      <c r="Z9" s="6" t="n">
+      <c r="X9" s="6" t="n">
         <v>0.7520967627210666</v>
       </c>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>+/−/−</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -21677,62 +21617,56 @@
       <c r="I10" s="3" t="n">
         <v>2.874228729504188</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>0.4973466981226321</v>
+      <c r="J10" s="3" t="n">
+        <v>63.77396063075215</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>63.77396063075215</v>
+        <v>1.176221702618918</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.176221702618918</v>
+        <v>1.025269129117514</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.025269129117514</v>
+        <v>176.0445296840527</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>8.066707325737838</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>44.6278742320767</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>7.110262329708609</v>
       </c>
+      <c r="P10" s="6" t="n">
+        <v>0.6415698195756852</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>50.63104331549373</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.6415698195756852</v>
-      </c>
+        <v>1.00523602897502</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.00523602897502</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="3" t="n">
         <v>-15.43998704357021</v>
       </c>
+      <c r="T10" s="3" t="n">
+        <v>-70.92126788487391</v>
+      </c>
+      <c r="U10" s="4" t="inlineStr"/>
       <c r="V10" s="3" t="n">
-        <v>-70.92126788487391</v>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="3" t="n">
         <v>11.8745387194912</v>
       </c>
-      <c r="Y10" s="3" t="n">
+      <c r="W10" s="3" t="n">
         <v>48466000000</v>
       </c>
-      <c r="Z10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.8221728149617376</v>
       </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>1.445703017504343</v>
+      </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.445703017504343</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -21768,64 +21702,58 @@
       <c r="I11" s="3" t="n">
         <v>2.801826670041789</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.04113956762544765</v>
+      <c r="J11" s="3" t="n">
+        <v>62.37217599955009</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>62.37217599955009</v>
+        <v>1.196908941742928</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.196908941742928</v>
+        <v>1.043893104104183</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.043893104104183</v>
+        <v>165.7603250430383</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>8.008627722283782</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>44.95152134470055</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>8.271098269242337</v>
       </c>
+      <c r="P11" s="6" t="n">
+        <v>0.6740053739685504</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>43.5250541441067</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.6740053739685504</v>
-      </c>
+        <v>1.054859540622612</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.054859540622612</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="3" t="n">
         <v>5.223806388466311</v>
       </c>
+      <c r="T11" s="3" t="n">
+        <v>199.0393097637393</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>0.3201193552060664</v>
+      </c>
       <c r="V11" s="3" t="n">
-        <v>199.0393097637393</v>
-      </c>
-      <c r="W11" s="6" t="n">
-        <v>0.3201193552060664</v>
-      </c>
-      <c r="X11" s="3" t="n">
         <v>1.966702005227392</v>
       </c>
-      <c r="Y11" s="3" t="n">
+      <c r="W11" s="3" t="n">
         <v>12521000000</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="X11" s="6" t="n">
         <v>0.7906342771404049</v>
       </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>1.574139724597159</v>
+      </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.574139724597159</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>

--- a/data/600104_上汽集团_财务数据.xlsx
+++ b/data/600104_上汽集团_财务数据.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务分析指标" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量校验" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并报表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42962,4 +42963,2123 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>营业利润率</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>净利润率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>净资产收益率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>存货周转率</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总资产周转率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>应收账款周转率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>流动比率</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>速动比率</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>利息保障倍数</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>货币资金占比</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>营业收入增长率</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>营业利润增长率</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>净利润增长率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2016Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.01564895731682214</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.06733870751303901</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06223789262612191</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.04222425925185851</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.586539955842715</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3279731842195368</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.475499091764406</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.128005797218141</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.927011413273214</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5714809615219322</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1522925440984061</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.7551401780327486</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.7467382385417809</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.7412981717540452</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.01009302050661876</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.06611538702175732</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.06155130070870031</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.08375271768650056</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.706131851425669</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6668260075382328</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.858504222815823</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.119922218810766</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9313847098556954</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5788666468643405</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.155337600540487</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8951909482832519</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8607616280965293</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8742837046064997</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2016Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.01020423229331813</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.06723593545661664</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06162332492353984</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1282630096224047</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13.33476673184626</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9883704128531929</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14.50678750698762</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.119458396195787</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9318488245516873</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5814099011645191</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1578725231490826</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5127419800871331</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5383804998703541</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.5145121141398024</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017年报</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.009998500607533822</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.06306689091823002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.05491529270380993</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1680578037572587</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18.78121494655508</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.352766136304409</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23.59772042044199</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9973808933097682</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7930777828648014</v>
+      </c>
+      <c r="K5" t="n">
+        <v>39.81108628557008</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6239204016955689</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1680794103378837</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.637816508443986</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5362617383194055</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4595313230490157</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.01047499470699509</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.06582595485412888</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05967728684278013</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.03747826936018183</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.855438122257251</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2860691678939741</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.24379636660984</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.179768407399731</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9870397732211027</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5822019624606041</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1789740465223106</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.7748562175643711</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.7650065788479896</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.7553328148909721</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.007575586844174809</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.06205356111161432</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05622475888931</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0757467526728641</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.891409761476763</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6174131351744303</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.00430473563753</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.098667622596494</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9223618294809964</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6134028147512945</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1698352643325056</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.019522668065075</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.903786638215488</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.9026866181533186</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.007616954125065134</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.06124405377391295</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05592460775643819</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1169217932141747</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.43745553399547</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9284730004034165</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14.4985261655504</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.070654144010545</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8815740199823244</v>
+      </c>
+      <c r="K8" t="n">
+        <v>30.01552285795638</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6047939441043777</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1714166141620026</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5339845240916912</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5139732353609927</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5257954770987039</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018年报</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00669759207174736</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06046894217477757</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05453271095918895</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.160049471899968</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15.49772809477422</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.237029526711384</v>
+      </c>
+      <c r="H9" t="n">
+        <v>21.21021308247294</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.094257378904864</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9068745881836154</v>
+      </c>
+      <c r="K9" t="n">
+        <v>29.80892706179819</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6362660807133641</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1581192432004292</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4832844327288734</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4645118189357149</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4463672520073458</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2018Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0120746194850565</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.06655392932011533</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.05979084408534843</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04141861281335407</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.193515974337354</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3074146679939002</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.56984488937792</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.045899710602998</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8448373419346477</v>
+      </c>
+      <c r="K10" t="n">
+        <v>24.1073481435166</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6174233375830368</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1709991276924109</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.7354150791941285</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.7087899095772953</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.7099033686574419</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01001014702667391</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.06569108100698635</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0585166669474072</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0834964025449387</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.161609597560185</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6172586513448217</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.93061610920921</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.057352311374228</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8615644287693665</v>
+      </c>
+      <c r="K11" t="n">
+        <v>22.17349817361936</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6390774400986728</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1594959852968544</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9466621180319597</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.9214243275373224</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.905177633174179</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2018Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.009624091095327247</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.06488325339414816</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05755192515363527</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1227063641071405</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11.23607828101192</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.901968730840887</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16.23056958360582</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.103719275977417</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9206827707482184</v>
+      </c>
+      <c r="K12" t="n">
+        <v>21.21460511138953</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6197212636556023</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1367752759718595</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4505600453994663</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4327219699592266</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4266452195357455</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019年报</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.004651770926130006</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.04881262988590911</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04269525217586299</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1065912752508207</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.81396935437127</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.043831110048982</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19.77155303243398</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.10448290093193</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9244106023513244</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20.91437949105034</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6457938170305403</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1505028063197827</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.24634170850607</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.06235872361225736</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.07539368318417772</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.003756416774362559</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.06334747246597343</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.05596254804529007</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.03332298058509221</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.54241630441153</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2400781874121564</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.378230248144649</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.172818403351191</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9665233415233419</v>
+      </c>
+      <c r="K14" t="n">
+        <v>23.74660452762063</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6234855117037053</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1402083721500055</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.762845200270147</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.6922280733249924</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.6891507557002787</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.005879184681369498</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.05577206463780296</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.04980614784179631</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.05702929912278776</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.518170265529048</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.470532973435881</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.858427289892135</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.143969513787276</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9621902974228607</v>
+      </c>
+      <c r="K15" t="n">
+        <v>14.96500549211622</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6336391413791866</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1596815289889622</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8769726948202368</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.6525149052337467</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.6704882604268663</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.005232233877712211</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.05465071671719447</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.04861000406398396</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.08630958206561039</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.841922523042397</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7235778447962573</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12.42436888950514</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.163783376751236</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9945656544487307</v>
+      </c>
+      <c r="K16" t="n">
+        <v>15.67495166674061</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.633945526474064</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1527365643549932</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5569302525127406</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5256267583257199</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.5195390364735812</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020年报</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.008970715326381384</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.04924675177483654</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.04036837014102843</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.08096181348328142</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11.33618420691767</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8395347523869946</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16.00076545134284</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.108226133525419</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8958550277558115</v>
+      </c>
+      <c r="K17" t="n">
+        <v>17.33560297924454</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6627834003143304</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1550605548093081</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2622524584856756</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.1374385778304639</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.04824254670915429</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.04590004738479436</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.02277583761252821</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01423046118459849</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.004400600704230605</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.787748374758167</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1175224044714737</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.489394548678837</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.139857252403704</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9387884150297883</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.826581893662751</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6277164817416342</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1680899485976017</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.8599668936638618</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.93523692070348</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.9506362115360747</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.01892700301666106</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.04523630837870264</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.04002444293682307</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.033829499688153</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.445338314278539</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3354035903620686</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.753931312566304</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.18220319748704</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.036280402000926</v>
+      </c>
+      <c r="K19" t="n">
+        <v>12.21500665138325</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6486614600334097</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.200702991494019</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.711314210917426</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.385086065469399</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.625813352845585</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.01401919407186525</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.04951575102912125</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.04409952915787992</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.06643088518836567</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.084448443494647</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5772628017245094</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10.09639278461793</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.186029929293998</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.039817553673538</v>
+      </c>
+      <c r="K20" t="n">
+        <v>15.61323412278225</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6410735081133803</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.1626884993940827</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.7654325029521587</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.9324458473285464</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.9451799057665371</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021年报</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.01425830509691961</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.05454132286548541</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.04466522589413468</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.09292576136598393</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13.86627081797102</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8621931615410484</v>
+      </c>
+      <c r="H21" t="n">
+        <v>15.21076553894353</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.134298754789471</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.969232914516911</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20.67914383795289</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6414409934094794</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1510770260970659</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.5679753774024539</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.7271161100584496</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5880889380336538</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0009084983329846752</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.06540675003389954</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.05165109968947029</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.02526380861930399</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.298561413675287</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2034621194645517</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.8957323317552</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.161068009422341</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.957765867784669</v>
+      </c>
+      <c r="K22" t="n">
+        <v>25.5941228733549</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.6407003341143848</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1746035112709184</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.7573275669493928</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.7089836781589398</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.7193723354026699</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.001145421701026939</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.06666191733905497</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.05340016383255589</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.04892936690962747</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.957732949563074</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4008521184384902</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.9833819003011</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.207925339366516</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.024787330316742</v>
+      </c>
+      <c r="K23" t="n">
+        <v>21.8534373020858</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.6273292909719211</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.18934165801713</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.9338052862027111</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.9709153576941147</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9992898452177459</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.002997088910685175</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.06497082507027352</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.05297049480950595</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.07442755406347436</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11.71247681288254</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6155724939456213</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12.04116714278723</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.193804337287095</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.031384616805256</v>
+      </c>
+      <c r="K24" t="n">
+        <v>24.05403316244669</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.628479842901698</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1693254014092642</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.5096802440367685</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4713823868653706</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.4975330371928521</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022年报</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.01899239535271646</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.03609247779929557</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.03168245209165525</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.05859925631033969</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11.03198877527641</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7770070145247109</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13.08447943926374</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.070205432234937</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8666813732248725</v>
+      </c>
+      <c r="K25" t="n">
+        <v>10.61603328975129</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6603397410582896</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1567073053720456</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.3391979755266545</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.2560511098900554</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.1990054868573603</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.0143689783774239</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.05075415166796459</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.04202579326123683</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.01981936054216045</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.431720368826628</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1854411037230115</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.944282321273973</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.184155094231157</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.007780022908918</v>
+      </c>
+      <c r="K26" t="n">
+        <v>17.44296193699246</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6352422032624031</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.165959401641786</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7548138133168978</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.6552130065714986</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.674768103104966</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.01872306645228305</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0396654559199304</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.03195866884971788</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.02488843716101122</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.645480912610987</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3268438598016124</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.346743867786844</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.196825900141085</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.010122761563208</v>
+      </c>
+      <c r="K27" t="n">
+        <v>11.88693734958519</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.6508064159594782</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1985724300688627</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.7254494701764993</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.3484756941480349</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.3121243873141597</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.01398247379909279</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.04024344641007237</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.03358637647539846</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.04593561819528121</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.194538720241976</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.5321067195557614</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.833583235665934</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.18062223522663</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9641931770494454</v>
+      </c>
+      <c r="K28" t="n">
+        <v>12.25214475222893</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.6598711293335758</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1982812422504009</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.6728061327621677</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.697181650808385</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.758004903442701</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年报</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.008247378394873772</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.03571619302566247</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.02762388270121447</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.05045484349016382</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.674367176653495</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.500733856799271</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11.47098069533215</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.1318299722344</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.9030067221978666</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8.523520117299569</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.4232595398970931</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.2631475926439848</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.1705923266923468</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.02543882262239605</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.03965321679287344</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.02933797613339827</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.009803196420695147</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.506714876851199</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.2967051878549227</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.159358851184015</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.114487729822608</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8868253996763076</v>
+      </c>
+      <c r="K30" t="n">
+        <v>7.583203184553912</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6414338133313082</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.1579911594308369</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.8063101503164399</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.7849595673715055</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.7942914742014903</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.01593238251939599</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.04294018385229922</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.03231982673070515</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.02515505143075749</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.46529009256902</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.334860529529987</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.953690449444919</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.148228330612556</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9095395042338864</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9.409953537130228</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.6414455170070194</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.1477428398483545</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.249505214323879</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.435973050668949</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.478140224335376</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.01098971397120097</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0428493325355414</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.03293605765206908</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.04017885177564135</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.49268647634065</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.536393783504685</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7.258269753802672</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.16474265108525</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9291352476139098</v>
+      </c>
+      <c r="K32" t="n">
+        <v>10.02467070883882</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.6395449567332984</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1434715634709544</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.6054193486270101</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.6020226593563507</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.6360293222702169</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024年报</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.01824855222582067</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0168974046359788</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.009499377506743888</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.005808801729941332</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.287688441141731</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.6431805546377047</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8.520049696397175</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.176221702618918</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9701052294361132</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.732955515616934</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.6377396063075215</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.206842655695126</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.2088785780200679</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.5232852116977869</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-0.6513367175349549</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.03121588899301209</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.02278208696340807</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.02053025606417867</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.009403620114487881</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.699612364028271</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1450226740093879</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.102248568373366</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.181110086206374</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9287843710325587</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.337719854993027</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.6364310903982592</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.150012088672497</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.7736692265737439</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.6948473760453513</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.5108491340252701</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.03467112494720825</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.03118232690441357</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0268422244459318</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.02301738045817778</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.05360620249791</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2867354705353209</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.111671340587476</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.188908227103815</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9254433416435393</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5.338751050306695</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.6440256290366504</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.1641532604060157</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.9936526221158635</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.728754740358448</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.606595406446302</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.03368937007940898</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0257652303126099</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.02009613435644215</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02384803987187698</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.733330183088347</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4352224605861272</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5.839000776866125</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.208096847958412</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9467702266969368</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.551730293757538</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.6333112112768056</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.1750863074240086</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.5145001034369534</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.2513961544031369</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.1338701687269204</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025年报</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.0043114642201183</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.03935959714703072</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.02699662168002747</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.03416730432810186</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7.793552753312876</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.6746517532267335</v>
+      </c>
+      <c r="H37" t="n">
+        <v>8.415191991681862</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.196908941742928</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.003464183265478</v>
+      </c>
+      <c r="K37" t="n">
+        <v>8.089494902302691</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.6237217599955009</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.1573056642994688</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.5397549357143085</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.352167368176281</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.068466538994294</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.01935335841444075</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0352966169718782</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.02909216218549991</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.01023359762086667</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.827963617311417</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1458857876316407</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.796463661582213</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.187381296683105</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9864085989609727</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6.091568361146559</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.6178510036687236</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.2090007742926222</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.7869231154874157</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.8089184411591674</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.770383592595693</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.01075551121049201</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.03513233709463935</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.02826254529099884</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.02049141889641081</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.972785039026507</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.3176939219673657</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.017118357176763</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.180722693934628</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.9918905563426922</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5.990465011800588</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.6149329611292303</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.2063766600371412</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.137827617822669</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.127877597431379</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.076863503228235</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.01247250197685101</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0349051974270285</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.02601628578645717</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0274225475181528</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.18724958919628</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.4937874115235477</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5.992955652726836</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.168963746939421</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9809493720875131</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6.629156661890965</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.6229922011777813</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.2025062337524537</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.5669963442348926</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.5568653066151028</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.4424541136757538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/600104_上汽集团_财务数据.xlsx
+++ b/data/600104_上汽集团_财务数据.xlsx
@@ -42971,7 +42971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43050,6 +43050,21 @@
           <t>净利润增长率</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>有息负债率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>经营现金流/营收</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>权益乘数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43102,6 +43117,15 @@
       <c r="P2" t="n">
         <v>-0.7412981717540452</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0.05112836527901136</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.02207714762254899</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.849379558071187</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43154,6 +43178,15 @@
       <c r="P3" t="n">
         <v>0.8742837046064997</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.05781890966838869</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.01391011564487839</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.928367169423014</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43206,6 +43239,15 @@
       <c r="P4" t="n">
         <v>0.5145121141398024</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.05771948046228434</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.03021830845668824</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.958913183943183</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43258,6 +43300,15 @@
       <c r="P5" t="n">
         <v>0.4595313230490157</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.06443382679159071</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02832357938069936</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.210921516852686</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43310,6 +43361,15 @@
       <c r="P6" t="n">
         <v>-0.7553328148909721</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0.07117588138469587</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.02627242006952313</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.909242769443503</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43362,6 +43422,15 @@
       <c r="P7" t="n">
         <v>0.9026866181533186</v>
       </c>
+      <c r="Q7" t="n">
+        <v>0.06595237758690281</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.03748450503580723</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.093141541331468</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43414,6 +43483,15 @@
       <c r="P8" t="n">
         <v>0.5257954770987039</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0.05811691447335139</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.03322753138450064</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.025518651991818</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43466,6 +43544,15 @@
       <c r="P9" t="n">
         <v>0.4463672520073458</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.08159868160506918</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.01011236478406895</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.339904168213373</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43518,6 +43605,15 @@
       <c r="P10" t="n">
         <v>-0.7099033686574419</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0.07525867275045293</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.06628841231404391</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.179754376082819</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43570,6 +43666,15 @@
       <c r="P11" t="n">
         <v>0.905177633174179</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0.08302441423097143</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.07228686640145059</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.341165417799422</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43622,6 +43727,15 @@
       <c r="P12" t="n">
         <v>0.4266452195357455</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0.08584066216904485</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.04423636193416609</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.182968430999432</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43674,6 +43788,15 @@
       <c r="P13" t="n">
         <v>-0.07539368318417772</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0.1032869322162214</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.05598344867560573</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.401386452651561</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43726,6 +43849,15 @@
       <c r="P14" t="n">
         <v>-0.6891507557002787</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.09734328061072131</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.09148763620995028</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.191819211248788</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43778,6 +43910,15 @@
       <c r="P15" t="n">
         <v>0.6704882604268663</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.09997718615584163</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.0003506236559266273</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.289200662706727</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43830,6 +43971,15 @@
       <c r="P16" t="n">
         <v>0.5195390364735812</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0.1080181155043963</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.04449745200937531</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.283125855971873</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43882,6 +44032,15 @@
       <c r="P17" t="n">
         <v>0.04824254670915429</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.1024085967707727</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.051889059592905</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.534811209405505</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43934,6 +44093,15 @@
       <c r="P18" t="n">
         <v>-0.9506362115360747</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0.1108417873749936</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.01625680621470208</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.223610531720309</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43986,6 +44154,15 @@
       <c r="P19" t="n">
         <v>6.625813352845585</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.1253720166663467</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.1069429140270493</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.37414613406758</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44038,6 +44215,15 @@
       <c r="P20" t="n">
         <v>0.9451799057665371</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.1120007093665947</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.07271270970973935</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.326863094465487</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44090,6 +44276,15 @@
       <c r="P21" t="n">
         <v>0.5880889380336538</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.1089011836326496</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.02844530028569374</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.349196782747814</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -44142,6 +44337,15 @@
       <c r="P22" t="n">
         <v>-0.7193723354026699</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.1147330712959686</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.01088876074159386</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.339699807626348</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -44194,6 +44398,15 @@
       <c r="P23" t="n">
         <v>0.9992898452177459</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0.1209776824976768</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.004444585552068806</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.201293595434369</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -44246,6 +44459,15 @@
       <c r="P24" t="n">
         <v>0.4975330371928521</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.1202691463555504</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.01289441492559568</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.19611607472495</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -44298,6 +44520,15 @@
       <c r="P25" t="n">
         <v>-0.1990054868573603</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0.1288325403213996</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.01318330709878555</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.545796715299713</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -44350,6 +44581,15 @@
       <c r="P26" t="n">
         <v>-0.674768103104966</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0.1176158639781503</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.0517207683739599</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.304228531046965</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -44402,6 +44642,15 @@
       <c r="P27" t="n">
         <v>0.3121243873141597</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.1362833497893698</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.01542202191854824</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.418603563241967</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -44454,6 +44703,15 @@
       <c r="P28" t="n">
         <v>0.758004903442701</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0.1318279134359449</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.009995362910565244</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.547091529498866</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -44506,6 +44764,15 @@
       <c r="P29" t="n">
         <v>0.1705923266923468</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.05829530688690309</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -44558,6 +44825,15 @@
       <c r="P30" t="n">
         <v>-0.7942914742014903</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.1317457856473117</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.07012073480293045</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.369460071289212</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -44610,6 +44886,15 @@
       <c r="P31" t="n">
         <v>1.478140224335376</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0.1294232586787303</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.02178505695242416</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.340191046427901</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -44662,6 +44947,15 @@
       <c r="P32" t="n">
         <v>0.6360293222702169</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0.1297318525036515</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.04153394814227013</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.331033011311568</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -44714,6 +45008,15 @@
       <c r="P33" t="n">
         <v>-0.6513367175349549</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0.139745053769395</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1128007260148941</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.325260561423013</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -44766,6 +45069,15 @@
       <c r="P34" t="n">
         <v>-0.5108491340252701</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0.1500902481929519</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.03270883458412496</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.316441959086055</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -44818,6 +45130,15 @@
       <c r="P35" t="n">
         <v>1.606595406446302</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0.1377493924150794</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.04084298423280371</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.39595743864094</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -44870,6 +45191,15 @@
       <c r="P36" t="n">
         <v>0.1338701687269204</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0.140574852455653</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.04453991470318967</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.263370408832531</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -44922,6 +45252,15 @@
       <c r="P37" t="n">
         <v>1.068466538994294</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0.09357565608249055</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.05309430999247533</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.213415123890607</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -44974,6 +45313,15 @@
       <c r="P38" t="n">
         <v>-0.770383592595693</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0.1415532008049192</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.02905286003034364</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.1754062152213</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -45026,6 +45374,15 @@
       <c r="P39" t="n">
         <v>1.076863503228235</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0.1206483611100008</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.07147267293244366</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.134685653329721</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -45077,6 +45434,15 @@
       </c>
       <c r="P40" t="n">
         <v>0.4424541136757538</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1089384052204361</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.06924620075103312</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.189091881173377</v>
       </c>
     </row>
   </sheetData>
